--- a/models/Three_Statement_Model_Fintech_SoFi.xlsx
+++ b/models/Three_Statement_Model_Fintech_SoFi.xlsx
@@ -31,12 +31,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="471">
   <si>
     <t xml:space="preserve">SOFI TECHNOLOGIES, INC.  (NASDAQ: SOFI)</t>
   </si>
   <si>
-    <t xml:space="preserve">Three-Statement Financial Model — Fintech — Digital Banking &amp; Lending (Bank Holding Company)</t>
+    <t xml:space="preserve">Three-Statement Financial Model; Fintech; Digital Banking &amp; Lending (Bank Holding Company)</t>
   </si>
   <si>
     <t xml:space="preserve">Integrated Income Statement · Balance Sheet · Cash Flow · driver-based forecast · regional scenarios · live market data</t>
@@ -63,16 +63,16 @@
     <t xml:space="preserve">HOW TO USE THIS MODEL</t>
   </si>
   <si>
-    <t xml:space="preserve">1.  Start on the Revenue Drivers and Assumptions tabs — every blue cell is an input; yellow cells are the key levers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.  Flip the scenario selector on Regional Breakdown (1 = Standard · 2 = Best Case · 3 = Low Case) — the whole model re-runs, including EPS, cash and the benchmarking tab.</t>
+    <t xml:space="preserve">1.  Start on the Revenue Drivers and Assumptions tabs; every blue cell is an input; yellow cells are the key levers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.  Flip the scenario selector on Regional Breakdown (1 = Standard · 2 = Best Case · 3 = Low Case); the whole model re-runs, including EPS, cash and the benchmarking tab.</t>
   </si>
   <si>
     <t xml:space="preserve">3.  Check Budget vs Actual for FY2025 performance vs guidance; rows over the 10% threshold flag automatically.</t>
   </si>
   <si>
-    <t xml:space="preserve">4.  Keep market data current: run refresh_market_data.py in this folder (or use the dashboard ⟳ button) — stamps update on Market Inputs and the refresh is logged in Version History.</t>
+    <t xml:space="preserve">4.  Keep market data current: run refresh_market_data.py in this folder (or use the dashboard ⟳ button); stamps update on Market Inputs and the refresh is logged in Version History.</t>
   </si>
   <si>
     <t xml:space="preserve">5.  For a browser walkthrough or a one-page memo, open Finance_AI_Dashboard.html and use Export memo (PDF).</t>
@@ -93,19 +93,19 @@
     <t xml:space="preserve">COLOR CONVENTIONS</t>
   </si>
   <si>
-    <t xml:space="preserve">Blue — hardcoded input (historical figures as reported; forecast assumptions)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black — formula / calculation          Green — direct link to another sheet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yellow fill — key assumption levers to flex</t>
+    <t xml:space="preserve">Blue = hardcoded input (historical figures as reported; forecast assumptions)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black = formula / calculation          Green = direct link to another sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yellow fill = key assumption levers to flex</t>
   </si>
   <si>
     <t xml:space="preserve">Every data input is cited on the Sources tab, with links and last-updated dates.</t>
   </si>
   <si>
-    <t xml:space="preserve">SoFi Technologies, Inc. — Forecast Assumptions</t>
+    <t xml:space="preserve">SoFi Technologies, Inc.; Forecast Assumptions</t>
   </si>
   <si>
     <t xml:space="preserve">(USD in thousands, except per-share amounts) · FY2023A–FY2025A per SEC filings · FY2026E–FY2030E forecast</t>
@@ -177,13 +177,13 @@
     <t xml:space="preserve">Deposits replace higher-cost warehouse funding</t>
   </si>
   <si>
-    <t xml:space="preserve">    Loan origination/sales/servicing income growth % — OUTPUT (driven by Revenue Drivers tab)</t>
+    <t xml:space="preserve">    Loan origination/sales/servicing income growth %; OUTPUT (driven by Revenue Drivers tab)</t>
   </si>
   <si>
     <t xml:space="preserve">    Technology products &amp; solutions growth %</t>
   </si>
   <si>
-    <t xml:space="preserve">    Loan platform fees growth % — OUTPUT (driven by Revenue Drivers tab)</t>
+    <t xml:space="preserve">    Loan platform fees growth %; OUTPUT (driven by Revenue Drivers tab)</t>
   </si>
   <si>
     <t xml:space="preserve">Capital-light third-party origination platform; FY25 grew 307%</t>
@@ -192,7 +192,7 @@
     <t xml:space="preserve">    Other noninterest income growth %</t>
   </si>
   <si>
-    <t xml:space="preserve">    Provision % of beginning amortized-cost loans — OUTPUT (driven by Revenue Drivers tab)</t>
+    <t xml:space="preserve">    Provision % of beginning amortized-cost loans; OUTPUT (driven by Revenue Drivers tab)</t>
   </si>
   <si>
     <t xml:space="preserve">    Technology &amp; product development % of net revenue</t>
@@ -249,7 +249,7 @@
     <t xml:space="preserve">Restricted cash, goodwill, intangibles, leases and noninterest-bearing deposits held flat in the forecast.</t>
   </si>
   <si>
-    <t xml:space="preserve">SoFi Technologies, Inc. — Revenue Drivers (Fintech)</t>
+    <t xml:space="preserve">SoFi Technologies, Inc.; Revenue Drivers (Fintech)</t>
   </si>
   <si>
     <t xml:space="preserve">Origination-driven fee &amp; credit build (volumes in $ millions; income in USD thousands) · drives loan fee lines and provision on the Income Statement</t>
@@ -306,10 +306,10 @@
     <t xml:space="preserve">Credit quality &amp; provision</t>
   </si>
   <si>
-    <t xml:space="preserve">    90-day delinquency rate — personal loans %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Annualized net charge-off rate — personal loans %</t>
+    <t xml:space="preserve">    90-day delinquency rate · personal loans %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Annualized net charge-off rate · personal loans %</t>
   </si>
   <si>
     <t xml:space="preserve">    Credit-loss rate on amortized-cost book %</t>
@@ -330,13 +330,13 @@
     <t xml:space="preserve">FY2024–FY2025 origination volumes and credit metrics per SoFi Q4 earnings releases; FY2023 volumes not restated on this basis (left blank).</t>
   </si>
   <si>
-    <t xml:space="preserve">Delinquency and charge-off rows are leading indicators that inform the credit-loss rate input; most of SoFi's book is carried at fair value, where credit is absorbed through valuation marks — the provision applies to the amortized-cost book.</t>
+    <t xml:space="preserve">Delinquency and charge-off rows are leading indicators that inform the credit-loss rate input; most of SoFi's book is carried at fair value, where credit is absorbed through valuation marks; the provision applies to the amortized-cost book.</t>
   </si>
   <si>
     <t xml:space="preserve">Interest income is driven separately on the Assumptions tab (yield on earning assets); loan growth assumptions there govern balance-sheet loan balances.</t>
   </si>
   <si>
-    <t xml:space="preserve">SoFi Technologies, Inc. — Regional Breakdown &amp; Scenarios</t>
+    <t xml:space="preserve">SoFi Technologies, Inc.; Regional Breakdown &amp; Scenarios</t>
   </si>
   <si>
     <t xml:space="preserve">Revenue, growth and customers by region (USD in thousands unless noted) · regional scenario toggle feeds the Income Statement · base = noninterest (fee) revenue</t>
@@ -363,25 +363,25 @@
     <t xml:space="preserve">BASE NONINTEREST (FEE) REVENUE BY REGION ($000s)</t>
   </si>
   <si>
-    <t xml:space="preserve">    Technology products &amp; solutions — base path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Other noninterest income — base path</t>
+    <t xml:space="preserve">    Technology products &amp; solutions · base path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Other noninterest income · base path</t>
   </si>
   <si>
     <t xml:space="preserve">    Base noninterest (fee) revenue before regional split</t>
   </si>
   <si>
-    <t xml:space="preserve">    North America — base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Europe — base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Asia Pacific — base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Other / rest of world — base</t>
+    <t xml:space="preserve">    North America · base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Europe · base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Asia Pacific · base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Other / rest of world · base</t>
   </si>
   <si>
     <t xml:space="preserve">    Total base (sum of regions)</t>
@@ -402,40 +402,40 @@
     <t xml:space="preserve">SCENARIO GROWTH DELTAS (added to base regional growth)</t>
   </si>
   <si>
-    <t xml:space="preserve">    Best Case — North America</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Best Case — Europe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Best Case — Asia Pacific</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Low Case — North America</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Low Case — Europe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Low Case — Asia Pacific</t>
+    <t xml:space="preserve">    Best Case · North America</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Best Case · Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Best Case · Asia Pacific</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Low Case · North America</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Low Case · Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Low Case · Asia Pacific</t>
   </si>
   <si>
     <t xml:space="preserve">SCENARIO NONINTEREST (FEE) REVENUE BY REGION ($000s)</t>
   </si>
   <si>
-    <t xml:space="preserve">    North America — scenario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Europe — scenario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Asia Pacific — scenario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Other / rest of world — scenario (no delta)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL — SCENARIO ($000s)</t>
+    <t xml:space="preserve">    North America · scenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Europe · scenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Asia Pacific · scenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Other / rest of world · scenario (no delta)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL · SCENARIO ($000s)</t>
   </si>
   <si>
     <t xml:space="preserve">    Scenario total growth %</t>
@@ -450,16 +450,16 @@
     <t xml:space="preserve">SCENARIO IMPACT DASHBOARD (flips with the selector)</t>
   </si>
   <si>
-    <t xml:space="preserve">    Total net revenue — scenario ($000s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Net income — scenario ($000s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Diluted EPS — scenario ($)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Ending cash — scenario ($000s)</t>
+    <t xml:space="preserve">    Total net revenue · scenario ($000s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Net income · scenario ($000s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Diluted EPS · scenario ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Ending cash · scenario ($000s)</t>
   </si>
   <si>
     <t xml:space="preserve">    Revenue CAGR FY2025A → FY2030E (scenario)</t>
@@ -486,16 +486,16 @@
     <t xml:space="preserve">    Other customer mix % (balancing)</t>
   </si>
   <si>
-    <t xml:space="preserve">    North America — customers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Europe — customers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Asia Pacific — customers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Other — customers</t>
+    <t xml:space="preserve">    North America · customers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Europe · customers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Asia Pacific · customers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Other · customers</t>
   </si>
   <si>
     <t xml:space="preserve">Check: regional mix sums to 100% (must be 0)</t>
@@ -504,7 +504,7 @@
     <t xml:space="preserve">Check: scenario total ties to Income Statement (must be 0)</t>
   </si>
   <si>
-    <t xml:space="preserve">•  SoFi is a U.S. deposit-funded bank — net interest income is domestic by construction, so the regional split and scenario apply to NONINTEREST (FEE) REVENUE only (lending fees, tech platform, loan platform). The 10-K shows 93–96% of total net revenue is U.S.; the foreign remainder is principally Latin America (Galileo), captured in "Other."</t>
+    <t xml:space="preserve">•  SoFi is a U.S. deposit-funded bank; net interest income is domestic by construction, so the regional split and scenario apply to NONINTEREST (FEE) REVENUE only (lending fees, tech platform, loan platform). The 10-K shows 93–96% of total net revenue is U.S.; the foreign remainder is principally Latin America (Galileo), captured in "Other."</t>
   </si>
   <si>
     <t xml:space="preserve">•  The scenario scaling factor multiplies the four noninterest income lines on the Income Statement; net interest income continues to be driven by balance-sheet growth and rates on the Assumptions tab.</t>
@@ -513,7 +513,7 @@
     <t xml:space="preserve">•  Members (7.5M / 10.1M / 13.7M at FY23–FY25 per Q4 releases) are effectively all U.S.; the regional member rows become meaningful only if international consumer expansion is modeled.</t>
   </si>
   <si>
-    <t xml:space="preserve">SoFi Technologies, Inc. — Statement of Operations</t>
+    <t xml:space="preserve">SoFi Technologies, Inc.; Statement of Operations</t>
   </si>
   <si>
     <t xml:space="preserve">Interest income and expense</t>
@@ -609,7 +609,7 @@
     <t xml:space="preserve">Memo: depreciation and amortization</t>
   </si>
   <si>
-    <t xml:space="preserve">SoFi Technologies, Inc. — Balance Sheet</t>
+    <t xml:space="preserve">SoFi Technologies, Inc.; Balance Sheet</t>
   </si>
   <si>
     <t xml:space="preserve">Assets</t>
@@ -651,7 +651,7 @@
     <t xml:space="preserve">    Other assets</t>
   </si>
   <si>
-    <t xml:space="preserve">Includes loan platform program receivables — grew with the capital-light fee business</t>
+    <t xml:space="preserve">Includes loan platform program receivables; grew with the capital-light fee business</t>
   </si>
   <si>
     <t xml:space="preserve">Total assets</t>
@@ -714,7 +714,7 @@
     <t xml:space="preserve">Must be zero in every period</t>
   </si>
   <si>
-    <t xml:space="preserve">SoFi Technologies, Inc. — Statement of Cash Flows</t>
+    <t xml:space="preserve">SoFi Technologies, Inc.; Statement of Cash Flows</t>
   </si>
   <si>
     <t xml:space="preserve">Operating activities</t>
@@ -792,10 +792,10 @@
     <t xml:space="preserve">Net change in cash, equivalents and restricted cash</t>
   </si>
   <si>
-    <t xml:space="preserve">    Cash, equivalents and restricted cash — beginning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cash, equivalents and restricted cash — ending</t>
+    <t xml:space="preserve">    Cash, equivalents and restricted cash, beginning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash, equivalents and restricted cash, ending</t>
   </si>
   <si>
     <t xml:space="preserve">    Less: restricted cash</t>
@@ -807,7 +807,7 @@
     <t xml:space="preserve">Links to cash on the balance sheet; forecast holds restricted cash flat on the balance sheet</t>
   </si>
   <si>
-    <t xml:space="preserve">SoFi Technologies, Inc. — Budget vs Actual Variance</t>
+    <t xml:space="preserve">SoFi Technologies, Inc.; Budget vs Actual Variance</t>
   </si>
   <si>
     <t xml:space="preserve">FY2025 actual vs FY2025 budget (USD in thousands, except per-share) · Budget seeded from company guidance where published; all budget cells editable</t>
@@ -846,7 +846,7 @@
     <t xml:space="preserve">Total net revenue (GAAP)</t>
   </si>
   <si>
-    <t xml:space="preserve">Placeholder — replace with your budget</t>
+    <t xml:space="preserve">Placeholder · replace with your budget</t>
   </si>
   <si>
     <t xml:space="preserve">Adjusted net revenue</t>
@@ -879,7 +879,7 @@
     <t xml:space="preserve">•  Budget column is seeded with the midpoint of company guidance issued at the start of FY2025 where published (see Budget source).</t>
   </si>
   <si>
-    <t xml:space="preserve">•  Rows marked "Placeholder" carry illustrative budgets — overwrite them, or type your own number in the yellow Override column (it takes precedence).</t>
+    <t xml:space="preserve">•  Rows marked "Placeholder" carry illustrative budgets; overwrite them, or type your own number in the yellow Override column (it takes precedence).</t>
   </si>
   <si>
     <t xml:space="preserve">•  GAAP actuals pull live from the statement tabs (green); non-GAAP actuals are per the company's Q4 FY2025 earnings release.</t>
@@ -888,10 +888,10 @@
     <t xml:space="preserve">•  Rows turn red automatically when |Variance %| exceeds the threshold in B4.</t>
   </si>
   <si>
-    <t xml:space="preserve">SoFi Technologies, Inc. — Market Inputs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snapshot as of market close July 17, 2026 · All values are inputs (blue) — see REFRESH section to wire live updates</t>
+    <t xml:space="preserve">SoFi Technologies, Inc.; Market Inputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snapshot as of market close July 17, 2026 · All values are inputs (blue); see REFRESH section to wire live updates</t>
   </si>
   <si>
     <t xml:space="preserve">Data as of:</t>
@@ -939,7 +939,7 @@
     <t xml:space="preserve">30-year Treasury</t>
   </si>
   <si>
-    <t xml:space="preserve">EQUITY MARKET DATA — PEER SET</t>
+    <t xml:space="preserve">EQUITY MARKET DATA: PEER SET</t>
   </si>
   <si>
     <t xml:space="preserve">PLTR</t>
@@ -978,7 +978,7 @@
     <t xml:space="preserve">Selected EV / Revenue multiple (x)</t>
   </si>
   <si>
-    <t xml:space="preserve">Defaults to this company's current multiple — flex it or use a peer's</t>
+    <t xml:space="preserve">Defaults to this company's current multiple; flex it or use a peer's</t>
   </si>
   <si>
     <t xml:space="preserve">Model FY2026E revenue ($000s)</t>
@@ -1008,7 +1008,7 @@
     <t xml:space="preserve">Implied premium / (discount) to current market cap</t>
   </si>
   <si>
-    <t xml:space="preserve">REFRESH — MAKE THIS TAB LIVE (one-time setup, ~2 minutes in Excel)</t>
+    <t xml:space="preserve">REFRESH: MAKE THIS TAB LIVE (one-time setup, ~2 minutes in Excel)</t>
   </si>
   <si>
     <t xml:space="preserve">1.  Excel ▸ Data ▸ Get Data (Power Query) ▸ From Other Sources ▸ From Web.</t>
@@ -1020,19 +1020,19 @@
     <t xml:space="preserve">3.  Load the query to a new sheet; point the blue rate cells above at the latest row (e.g. =INDEX(...)).</t>
   </si>
   <si>
-    <t xml:space="preserve">4.  Share prices (JSON):  https://query1.finance.yahoo.com/v8/finance/chart/SOFI   — Power Query ▸ From Web, drill to chart.result.meta.regularMarketPrice.</t>
+    <t xml:space="preserve">4.  Share prices (JSON):  https://query1.finance.yahoo.com/v8/finance/chart/SOFI  ; Power Query ▸ From Web, drill to chart.result.meta.regularMarketPrice.</t>
   </si>
   <si>
     <t xml:space="preserve">5.  After setup, Data ▸ Refresh All re-pulls everything with one click.</t>
   </si>
   <si>
-    <t xml:space="preserve">6.  Until then this tab is a dated snapshot (see B4) — or ask Claude to refresh the numbers any time.</t>
+    <t xml:space="preserve">6.  Until then this tab is a dated snapshot (see B4); or ask Claude to refresh the numbers any time.</t>
   </si>
   <si>
     <t xml:space="preserve">Sources for this snapshot: Fed H.15 (Jul 17, 2026), NY Fed SOFR, stockanalysis.com / S&amp;P Global (Jul 17–19, 2026).</t>
   </si>
   <si>
-    <t xml:space="preserve">SoFi Technologies, Inc. — Competitor Benchmarking</t>
+    <t xml:space="preserve">SoFi Technologies, Inc.; Competitor Benchmarking</t>
   </si>
   <si>
     <t xml:space="preserve">Company column pulls live from this model (FY2025 actuals; FY2026E is scenario-aware) · comps per latest reported fiscal year, valuations as of July 17–20, 2026 · industry benchmarks: Clouded Judgement SaaS medians (7/10/26) and US bank norms</t>
@@ -1065,16 +1065,16 @@
     <t xml:space="preserve">SoFi's $3.6B revenue base is ~4x LendingClub but a fraction of Nu's LatAm franchise.</t>
   </si>
   <si>
-    <t xml:space="preserve">Revenue growth — FY2025 %</t>
+    <t xml:space="preserve">Revenue growth · FY2025 %</t>
   </si>
   <si>
     <t xml:space="preserve">~3–5%</t>
   </si>
   <si>
-    <t xml:space="preserve">35% growth is ~8x typical bank growth — between NU (45%) and LC (27%); the fee/platform mix shift is doing the work.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue growth — FY2026E (model, scenario-aware) %</t>
+    <t xml:space="preserve">35% growth is ~8x typical bank growth; between NU (45%) and LC (27%); the fee/platform mix shift is doing the work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue growth · FY2026E (model, scenario-aware) %</t>
   </si>
   <si>
     <t xml:space="preserve">n/a</t>
@@ -1083,28 +1083,28 @@
     <t xml:space="preserve">Model FY26E growth (scenario-aware) of ~31% is driven by deposits, loan platform volume and take rates on Revenue Drivers.</t>
   </si>
   <si>
-    <t xml:space="preserve">Net income margin — FY2025 %</t>
+    <t xml:space="preserve">Net income margin · FY2025 %</t>
   </si>
   <si>
     <t xml:space="preserve">~25–30%</t>
   </si>
   <si>
-    <t xml:space="preserve">13% net margin lags NU (18%) and big-bank norms — SoFi is still buying growth with marketing (30% of revenue).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return on equity — FY2025 %</t>
+    <t xml:space="preserve">13% net margin lags NU (18%) and big-bank norms; SoFi is still buying growth with marketing (30% of revenue).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return on equity · FY2025 %</t>
   </si>
   <si>
     <t xml:space="preserve">10–12%</t>
   </si>
   <si>
-    <t xml:space="preserve">~5–6% ROE is below the 10–12% bank benchmark and far from NU's 30% — the FY25 $3.2B capital raise inflated equity; grinding ROE toward double digits is the core bull case.</t>
+    <t xml:space="preserve">~5–6% ROE is below the 10–12% bank benchmark and far from NU's 30%; the FY25 $3.2B capital raise inflated equity; grinding ROE toward double digits is the core bull case.</t>
   </si>
   <si>
     <t xml:space="preserve">12–14x</t>
   </si>
   <si>
-    <t xml:space="preserve">26x forward earnings is ~2x the bank group and a premium even to NU (15x) — the market is paying for growth and the fee-mix shift, not current profitability.</t>
+    <t xml:space="preserve">26x forward earnings is ~2x the bank group and a premium even to NU (15x); the market is paying for growth and the fee-mix shift, not current profitability.</t>
   </si>
   <si>
     <t xml:space="preserve">Price / tangible book value (x)</t>
@@ -1113,7 +1113,7 @@
     <t xml:space="preserve">1.5–2.5x</t>
   </si>
   <si>
-    <t xml:space="preserve">~2.5x tangible book is at the top of the traditional bank range but half of NU — consistent with transition-story status.</t>
+    <t xml:space="preserve">~2.5x tangible book is at the top of the traditional bank range but half of NU; consistent with transition-story status.</t>
   </si>
   <si>
     <t xml:space="preserve">EV / Revenue (x)</t>
@@ -1131,19 +1131,19 @@
     <t xml:space="preserve">•  US bank norms (mid-2026): industry trailing P/E 14.8x, large-cap forward P/E ~12–14x · ROE benchmark 10–12% (≈ cost of equity) · P/TBV ~1.5–2.5x for large caps, ~1x is the fair-value floor · S&amp;P 500 forward P/E 20.9x for context.</t>
   </si>
   <si>
-    <t xml:space="preserve">•  High-growth digital banks command premiums when growth comes WITH returns: Nu holds ~30% ROE at 15x forward earnings — growth alone does not sustain a premium multiple.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAKEAWAYS — WHAT THIS COMPARISON MEANS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">•  SoFi grows like a fintech (35%) but still earns like a sub-scale bank (~5–6% ROE vs the 10–12% benchmark) — the valuation (26x fwd P/E, ~2.5x TBV) prepays the convergence.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">•  Nu Holdings is the existence proof the market is underwriting: 45% growth WITH 30% ROE at only 15x forward earnings — SoFi trades richer on every earnings-based multiple with weaker current returns.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">•  LendingClub is the floor comp: similar lending DNA at ~1x revenue and 1.6x TBV — SoFi's premium is entirely the deposit franchise, member growth (13.7M) and the capital-light loan platform.</t>
+    <t xml:space="preserve">•  High-growth digital banks command premiums when growth comes WITH returns: Nu holds ~30% ROE at 15x forward earnings; growth alone does not sustain a premium multiple.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAKEAWAYS: WHAT THIS COMPARISON MEANS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  SoFi grows like a fintech (35%) but still earns like a sub-scale bank (~5–6% ROE vs the 10–12% benchmark); the valuation (26x fwd P/E, ~2.5x TBV) prepays the convergence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  Nu Holdings is the existence proof the market is underwriting: 45% growth WITH 30% ROE at only 15x forward earnings; SoFi trades richer on every earnings-based multiple with weaker current returns.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  LendingClub is the floor comp: similar lending DNA at ~1x revenue and 1.6x TBV; SoFi's premium is entirely the deposit franchise, member growth (13.7M) and the capital-light loan platform.</t>
   </si>
   <si>
     <t xml:space="preserve">•  Watch ROE in the model: flip the Best Case regional scenario and provision/marketing assumptions to see how quickly net income closes the gap to the bank benchmark.</t>
@@ -1152,7 +1152,7 @@
     <t xml:space="preserve">Sources: company Q4/FY earnings releases and 10-Ks (SEC EDGAR); stockanalysis.com / S&amp;P Global valuations Jul 17–20, 2026; cloudedjudgement.substack.com 7/10/26; multiples.vc Jul 2026. Comp forward P/Es are consensus (non-GAAP) based.</t>
   </si>
   <si>
-    <t xml:space="preserve">SoFi Technologies, Inc. — Version History</t>
+    <t xml:space="preserve">SoFi Technologies, Inc.; Version History</t>
   </si>
   <si>
     <t xml:space="preserve">Log of every assumptions refresh: what changed, when, and why. Add a new row each time inputs are updated.</t>
@@ -1185,7 +1185,7 @@
     <t xml:space="preserve">Initial build: FY2023–FY2025 actuals per SEC filings; FY2026–FY2030 top-down forecast; Assumptions, Income Statement, Balance Sheet, Cash Flow and Cover with sheet links.</t>
   </si>
   <si>
-    <t xml:space="preserve">Portfolio work sample — integrated three-statement model with balance and cash tie-out checks.</t>
+    <t xml:space="preserve">Portfolio work sample: integrated three-statement model with balance and cash tie-out checks.</t>
   </si>
   <si>
     <t xml:space="preserve">1.1</t>
@@ -1206,7 +1206,7 @@
     <t xml:space="preserve">Rebuilt revenue as a bottoms-up Revenue Drivers tab (loan originations × take rates, loan platform volume, delinquency-informed provision); superseded top-down assumption rows relabeled as OUTPUT.</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit-economics realism — forecast driven by operating metrics rather than a single growth rate.</t>
+    <t xml:space="preserve">Unit-economics realism: forecast driven by operating metrics rather than a single growth rate.</t>
   </si>
   <si>
     <t xml:space="preserve">1.3</t>
@@ -1224,7 +1224,7 @@
     <t xml:space="preserve">Added Competitor Benchmarking tab vs Nu Holdings and LendingClub + US bank norms; company column pulls live from the model with interpretation and takeaways.</t>
   </si>
   <si>
-    <t xml:space="preserve">Relative context — absolute metrics only matter versus peers and industry medians.</t>
+    <t xml:space="preserve">Relative context: absolute metrics only matter versus peers and industry medians.</t>
   </si>
   <si>
     <t xml:space="preserve">1.5</t>
@@ -1242,7 +1242,7 @@
     <t xml:space="preserve">Added this Version History tab.</t>
   </si>
   <si>
-    <t xml:space="preserve">Change auditability — every future assumptions refresh gets logged here.</t>
+    <t xml:space="preserve">Change auditability: every future assumptions refresh gets logged here.</t>
   </si>
   <si>
     <t xml:space="preserve">1.7</t>
@@ -1260,13 +1260,22 @@
     <t xml:space="preserve">Applied workbook protection: all formulas, labels and structure locked with a password on every tab; blue/yellow input cells (assumptions, scenario selector, budget overrides) remain editable so the model stays interactive.</t>
   </si>
   <si>
-    <t xml:space="preserve">Distribution protection — models are downloadable from the public portfolio site; viewers can flex inputs but cannot alter or break the model.</t>
+    <t xml:space="preserve">Distribution protection: models are downloadable from the public portfolio site; viewers can flex inputs but cannot alter or break the model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copy edit across all tabs: punctuation and separator cleanup for a natural reading style; no numbers or formulas changed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Readability pass ahead of public distribution.</t>
   </si>
   <si>
     <t xml:space="preserve">How to log a refresh: add a row (yellow cells above are ready) with the new version number, date, your name, the cells/tabs you changed (e.g. "Assumptions F7: FY27 revenue growth 45% → 40% after Q1 FY27 print"), and the reason. Keep one row per refresh so the audit trail stays readable.</t>
   </si>
   <si>
-    <t xml:space="preserve">Sofi Technologies, Inc. — Data Sources &amp; Citations</t>
+    <t xml:space="preserve">Sofi Technologies, Inc.; Data Sources &amp; Citations</t>
   </si>
   <si>
     <t xml:space="preserve">Every input in this model, where it comes from, and how current it is. Click "Open ↗" for the underlying source. Refresh stamps also appear on Market Inputs; refreshes are logged in Version History.</t>
@@ -1302,7 +1311,7 @@
     <t xml:space="preserve">SoFi Q4 FY2025 earnings release, 8-K Ex. 99.1, filed Jan 30, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Static actuals — restate on next annual filing</t>
+    <t xml:space="preserve">Static actuals · restate on next annual filing</t>
   </si>
   <si>
     <t xml:space="preserve">FY2023 statements; FY2024 originations &amp; credit metrics</t>
@@ -1332,7 +1341,7 @@
     <t xml:space="preserve">FY2025 Form 10-K, geographic disclosure</t>
   </si>
   <si>
-    <t xml:space="preserve">Static — update on next 10-K</t>
+    <t xml:space="preserve">Static · update on next 10-K</t>
   </si>
   <si>
     <t xml:space="preserve">GUIDANCE &amp; BUDGET</t>
@@ -1347,7 +1356,7 @@
     <t xml:space="preserve">Issued with Q4 FY2024 release, Jan 27, 2025 ($3,200–3,275M adj. net revenue)</t>
   </si>
   <si>
-    <t xml:space="preserve">Static — replace with FY2026 guidance next cycle</t>
+    <t xml:space="preserve">Static · replace with FY2026 guidance next cycle</t>
   </si>
   <si>
     <t xml:space="preserve">MARKET DATA</t>
@@ -1383,7 +1392,7 @@
     <t xml:space="preserve">Market Inputs · Competitor Benchmarking</t>
   </si>
   <si>
-    <t xml:space="preserve">stockanalysis.com (SOFI) — data: S&amp;P Global Market Intelligence, close Jul 17, 2026</t>
+    <t xml:space="preserve">stockanalysis.com (SOFI); data: S&amp;P Global Market Intelligence, close Jul 17, 2026</t>
   </si>
   <si>
     <t xml:space="preserve">refresh_market_data.py scales by live price ratio</t>
@@ -1392,7 +1401,7 @@
     <t xml:space="preserve">VALUATION &amp; INDUSTRY BENCHMARKS</t>
   </si>
   <si>
-    <t xml:space="preserve">Comp fundamentals — Nu Holdings (FY2025)</t>
+    <t xml:space="preserve">Comp fundamentals · Nu Holdings (FY2025)</t>
   </si>
   <si>
     <t xml:space="preserve">Competitor Benchmarking</t>
@@ -1401,10 +1410,10 @@
     <t xml:space="preserve">Nu Holdings Q4/FY2025 results, Feb 25, 2026 (IFRS 20-F: $15.8B revenue)</t>
   </si>
   <si>
-    <t xml:space="preserve">Static — update after comp earnings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comp fundamentals — LendingClub (FY2025)</t>
+    <t xml:space="preserve">Static · update after comp earnings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comp fundamentals · LendingClub (FY2025)</t>
   </si>
   <si>
     <t xml:space="preserve">LendingClub Q4/FY2025 results, Jan 28, 2026</t>
@@ -1416,7 +1425,7 @@
     <t xml:space="preserve">Simply Wall St US banks industry data; GuruFocus / Macrotrends large-cap bank multiples, Jul 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Manual — ask Claude to refresh</t>
+    <t xml:space="preserve">Manual · ask Claude to refresh</t>
   </si>
   <si>
     <t xml:space="preserve">FORECAST ASSUMPTIONS</t>
@@ -1434,7 +1443,7 @@
     <t xml:space="preserve">Every change is logged on the Version History tab</t>
   </si>
   <si>
-    <t xml:space="preserve">Conventions: "Static actuals" never change once filed (restated only if the company restates). Market data carries dual stamps — "Data as of" (the market close the values describe) and "Last refreshed" (when the file was last updated). Analyst assumptions are the author's judgment; the Version History tab is the audit trail.</t>
+    <t xml:space="preserve">Conventions: "Static actuals" never change once filed (restated only if the company restates). Market data carries dual stamps; "Data as of" (the market close the values describe) and "Last refreshed" (when the file was last updated). Analyst assumptions are the author's judgment; the Version History tab is the audit trail.</t>
   </si>
 </sst>
 </file>
@@ -1999,7 +2008,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -2352,20 +2361,20 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="7" t="str">
-        <f aca="false">HYPERLINK("Finance_AI_Dashboard.html","▸  Interactive dashboard  —  toggle industry, scenario and region in your browser (same folder)")</f>
-        <v>▸  Interactive dashboard  —  toggle industry, scenario and region in your browser (same folder)</v>
+        <f aca="false">HYPERLINK("Finance_AI_Dashboard.html","▸  Interactive dashboard  ·  toggle industry, scenario and region in your browser (same folder)")</f>
+        <v>▸  Interactive dashboard  ·  toggle industry, scenario and region in your browser (same folder)</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="str">
-        <f aca="false">HYPERLINK("README.md","▸  Portfolio README  —  overview of all three models and how they fit together")</f>
-        <v>▸  Portfolio README  —  overview of all three models and how they fit together</v>
+        <f aca="false">HYPERLINK("README.md","▸  Portfolio README  ·  overview of all three models and how they fit together")</f>
+        <v>▸  Portfolio README  ·  overview of all three models and how they fit together</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="7" t="str">
-        <f aca="false">HYPERLINK("refresh_market_data.py","▸  Market-data refresh script  —  run to update prices, rates and refresh stamps everywhere")</f>
-        <v>▸  Market-data refresh script  —  run to update prices, rates and refresh stamps everywhere</v>
+        <f aca="false">HYPERLINK("refresh_market_data.py","▸  Market-data refresh script  ·  run to update prices, rates and refresh stamps everywhere")</f>
+        <v>▸  Market-data refresh script  ·  run to update prices, rates and refresh stamps everywhere</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2375,68 +2384,68 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Assumptions'!A1","▸  Assumptions  —  Margin, tax, working-capital and financing drivers")</f>
-        <v>▸  Assumptions  —  Margin, tax, working-capital and financing drivers</v>
+        <f aca="false">HYPERLINK("#'Assumptions'!A1","▸  Assumptions  ·  Margin, tax, working-capital and financing drivers")</f>
+        <v>▸  Assumptions  ·  Margin, tax, working-capital and financing drivers</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Revenue Drivers'!A1","▸  Revenue Drivers  —  Bottoms-up sector build driving revenue and key costs")</f>
-        <v>▸  Revenue Drivers  —  Bottoms-up sector build driving revenue and key costs</v>
+        <f aca="false">HYPERLINK("#'Revenue Drivers'!A1","▸  Revenue Drivers  ·  Bottoms-up sector build driving revenue and key costs")</f>
+        <v>▸  Revenue Drivers  ·  Bottoms-up sector build driving revenue and key costs</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Regional Breakdown'!A1","▸  Regional Breakdown  —  NA / Europe / APAC splits and the Standard / Best / Low case selector")</f>
-        <v>▸  Regional Breakdown  —  NA / Europe / APAC splits and the Standard / Best / Low case selector</v>
+        <f aca="false">HYPERLINK("#'Regional Breakdown'!A1","▸  Regional Breakdown  ·  NA / Europe / APAC splits and the Standard / Best / Low case selector")</f>
+        <v>▸  Regional Breakdown  ·  NA / Europe / APAC splits and the Standard / Best / Low case selector</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Income Statement'!A1","▸  Income Statement  —  Revenue build-down to EPS")</f>
-        <v>▸  Income Statement  —  Revenue build-down to EPS</v>
+        <f aca="false">HYPERLINK("#'Income Statement'!A1","▸  Income Statement  ·  Revenue build-down to EPS")</f>
+        <v>▸  Income Statement  ·  Revenue build-down to EPS</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Balance Sheet'!A1","▸  Balance Sheet  —  Assets, liabilities and equity, with balance check")</f>
-        <v>▸  Balance Sheet  —  Assets, liabilities and equity, with balance check</v>
+        <f aca="false">HYPERLINK("#'Balance Sheet'!A1","▸  Balance Sheet  ·  Assets, liabilities and equity, with balance check")</f>
+        <v>▸  Balance Sheet  ·  Assets, liabilities and equity, with balance check</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Cash Flow'!A1","▸  Cash Flow  —  Indirect-method cash flow; ending cash links to the balance sheet")</f>
-        <v>▸  Cash Flow  —  Indirect-method cash flow; ending cash links to the balance sheet</v>
+        <f aca="false">HYPERLINK("#'Cash Flow'!A1","▸  Cash Flow  ·  Indirect-method cash flow; ending cash links to the balance sheet")</f>
+        <v>▸  Cash Flow  ·  Indirect-method cash flow; ending cash links to the balance sheet</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Budget vs Actual'!A1","▸  Budget vs Actual  —  FY2025 vs guidance with automatic &gt;10% variance flagging")</f>
-        <v>▸  Budget vs Actual  —  FY2025 vs guidance with automatic &gt;10% variance flagging</v>
+        <f aca="false">HYPERLINK("#'Budget vs Actual'!A1","▸  Budget vs Actual  ·  FY2025 vs guidance with automatic &gt;10% variance flagging")</f>
+        <v>▸  Budget vs Actual  ·  FY2025 vs guidance with automatic &gt;10% variance flagging</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Market Inputs'!A1","▸  Market Inputs  —  Rates and valuation multiples with refresh stamps")</f>
-        <v>▸  Market Inputs  —  Rates and valuation multiples with refresh stamps</v>
+        <f aca="false">HYPERLINK("#'Market Inputs'!A1","▸  Market Inputs  ·  Rates and valuation multiples with refresh stamps")</f>
+        <v>▸  Market Inputs  ·  Rates and valuation multiples with refresh stamps</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Competitor Benchmarking'!A1","▸  Competitor Benchmarking  —  Two public comps + peer median + industry benchmarks")</f>
-        <v>▸  Competitor Benchmarking  —  Two public comps + peer median + industry benchmarks</v>
+        <f aca="false">HYPERLINK("#'Competitor Benchmarking'!A1","▸  Competitor Benchmarking  ·  Two public comps + peer median + industry benchmarks")</f>
+        <v>▸  Competitor Benchmarking  ·  Two public comps + peer median + industry benchmarks</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Version History'!A1","▸  Version History  —  Audit log of every assumptions and data refresh")</f>
-        <v>▸  Version History  —  Audit log of every assumptions and data refresh</v>
+        <f aca="false">HYPERLINK("#'Version History'!A1","▸  Version History  ·  Audit log of every assumptions and data refresh")</f>
+        <v>▸  Version History  ·  Audit log of every assumptions and data refresh</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Sources'!A1","▸  Sources  —  Where every input comes from — citations, links, last-updated dates")</f>
-        <v>▸  Sources  —  Where every input comes from — citations, links, last-updated dates</v>
+        <f aca="false">HYPERLINK("#'Sources'!A1","▸  Sources  ·  Where every input comes from: citations, links, last-updated dates")</f>
+        <v>▸  Sources  ·  Where every input comes from: citations, links, last-updated dates</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3024,16 +3033,26 @@
         <v>409</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="70"/>
-      <c r="B14" s="70"/>
-      <c r="C14" s="70"/>
-      <c r="D14" s="70"/>
-      <c r="E14" s="70"/>
+    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="67" t="s">
+        <v>410</v>
+      </c>
+      <c r="B14" s="67" t="s">
+        <v>386</v>
+      </c>
+      <c r="C14" s="67" t="s">
+        <v>382</v>
+      </c>
+      <c r="D14" s="70" t="s">
+        <v>411</v>
+      </c>
+      <c r="E14" s="70" t="s">
+        <v>412</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -3066,37 +3085,37 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="71" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B4" s="71" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C4" s="71" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D4" s="71" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E4" s="71" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F4" s="71" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="72" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B5" s="73"/>
       <c r="C5" s="73"/>
@@ -3106,13 +3125,13 @@
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="68" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B6" s="68" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C6" s="68" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D6" s="74" t="str">
         <f aca="false">HYPERLINK("https://www.sec.gov/Archives/edgar/data/1818874/000181887426000008/a2025q4earningsrelease.htm","Open ↗")</f>
@@ -3122,18 +3141,18 @@
         <v>381</v>
       </c>
       <c r="F6" s="75" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="68" t="s">
+        <v>427</v>
+      </c>
+      <c r="B7" s="68" t="s">
         <v>424</v>
       </c>
-      <c r="B7" s="68" t="s">
-        <v>421</v>
-      </c>
       <c r="C7" s="68" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D7" s="74" t="str">
         <f aca="false">HYPERLINK("https://www.sec.gov/Archives/edgar/data/1818874/000181887425000006/q42024earningsrelease.htm","Open ↗")</f>
@@ -3143,18 +3162,18 @@
         <v>381</v>
       </c>
       <c r="F7" s="75" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="68" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B8" s="68" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C8" s="68" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="D8" s="74" t="str">
         <f aca="false">HYPERLINK("https://www.sec.gov/Archives/edgar/data/1818874/000181887426000013/R5.htm","Open ↗")</f>
@@ -3164,18 +3183,18 @@
         <v>381</v>
       </c>
       <c r="F8" s="75" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="68" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B9" s="68" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C9" s="68" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="D9" s="74" t="str">
         <f aca="false">HYPERLINK("https://www.sec.gov/Archives/edgar/data/1818874/000181887426000013/R131.htm","Open ↗")</f>
@@ -3185,12 +3204,12 @@
         <v>386</v>
       </c>
       <c r="F9" s="75" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="72" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B10" s="73"/>
       <c r="C10" s="73"/>
@@ -3200,13 +3219,13 @@
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="68" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B11" s="68" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C11" s="68" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D11" s="74" t="str">
         <f aca="false">HYPERLINK("https://www.sec.gov/Archives/edgar/data/1818874/000181887425000006/q42024earningsrelease.htm","Open ↗")</f>
@@ -3216,12 +3235,12 @@
         <v>386</v>
       </c>
       <c r="F11" s="75" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="72" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B12" s="73"/>
       <c r="C12" s="73"/>
@@ -3231,70 +3250,70 @@
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="68" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B13" s="68" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C13" s="68" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D13" s="74" t="str">
         <f aca="false">HYPERLINK("https://home.treasury.gov/resource-center/data-chart-center/interest-rates/","Open ↗")</f>
         <v>Open ↗</v>
       </c>
       <c r="E13" s="68" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F13" s="75" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="68" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B14" s="68" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C14" s="68" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="D14" s="74" t="str">
         <f aca="false">HYPERLINK("https://www.newyorkfed.org/markets/reference-rates/sofr","Open ↗")</f>
         <v>Open ↗</v>
       </c>
       <c r="E14" s="68" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F14" s="75" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="68" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B15" s="68" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C15" s="68" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="D15" s="74" t="str">
         <f aca="false">HYPERLINK("https://stockanalysis.com/stocks/sofi/statistics/","Open ↗")</f>
         <v>Open ↗</v>
       </c>
       <c r="E15" s="68" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F15" s="75" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="72" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B16" s="73"/>
       <c r="C16" s="73"/>
@@ -3304,13 +3323,13 @@
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="68" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B17" s="68" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C17" s="68" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D17" s="74" t="str">
         <f aca="false">HYPERLINK("https://international.nubank.com.br/company/nu-holdings-ltd-reports-fourth-quarter-and-full-year-2025-financial-results/","Open ↗")</f>
@@ -3320,18 +3339,18 @@
         <v>386</v>
       </c>
       <c r="F17" s="75" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="68" t="s">
+        <v>460</v>
+      </c>
+      <c r="B18" s="68" t="s">
         <v>457</v>
       </c>
-      <c r="B18" s="68" t="s">
-        <v>454</v>
-      </c>
       <c r="C18" s="68" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="D18" s="74" t="str">
         <f aca="false">HYPERLINK("https://ir.lendingclub.com/news/news-details/2026/LendingClub-Reports-Fourth-Quarter-and-Full-Year-2025-Results/default.aspx","Open ↗")</f>
@@ -3341,18 +3360,18 @@
         <v>386</v>
       </c>
       <c r="F18" s="75" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="68" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B19" s="68" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C19" s="68" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="D19" s="74" t="str">
         <f aca="false">HYPERLINK("https://simplywall.st/markets/us/financials/banks","Open ↗")</f>
@@ -3362,12 +3381,12 @@
         <v>386</v>
       </c>
       <c r="F19" s="75" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="72" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B20" s="73"/>
       <c r="C20" s="73"/>
@@ -3377,13 +3396,13 @@
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="68" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B21" s="68" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C21" s="68" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D21" s="76" t="s">
         <v>342</v>
@@ -3392,12 +3411,12 @@
         <v>386</v>
       </c>
       <c r="F21" s="75" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="18" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>
